--- a/manual-qa-repository/07-execution/TestCases-SMPortal.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-SMPortal.xlsx
@@ -9,13 +9,17 @@
     <sheet sheetId="3" name="Callback Requests - Master" state="visible" r:id="rId6"/>
     <sheet sheetId="5" name="Tower Heatmap - Master" state="visible" r:id="rId7"/>
     <sheet sheetId="4" name="Physical Allocation - Master" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Login - Exec" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Callback Requests - Exec" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Tower Heatmap - Exec" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Physical Allocation - Exec" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4827" uniqueCount="2499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7480" uniqueCount="2508">
   <si>
     <t>XR Portal — Sales Manager</t>
   </si>
@@ -8039,12 +8043,39 @@
   <si>
     <t>[VERIFY WITH DEV] A skeleton/loader is shown while GET /campaign/active is in flight, then resolves to the idle card or the search card. Confirm the loader exists on capture. (Source: baseline TC SM_PA_025.)</t>
   </si>
+  <si>
+    <t>TC ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Automation Status</t>
+  </si>
+  <si>
+    <t>Last Run Status</t>
+  </si>
+  <si>
+    <t>Execution Details</t>
+  </si>
+  <si>
+    <t>Actual Result (Run)</t>
+  </si>
+  <si>
+    <t>Screenshot Link</t>
+  </si>
+  <si>
+    <t>Not Automated</t>
+  </si>
+  <si>
+    <t>Automated</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -8080,6 +8111,23 @@
       <b/>
       <color rgb="00000000"/>
       <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -8128,7 +8176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -8151,6 +8199,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25268,4 +25328,8801 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G104"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D75" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D77" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D79" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D81" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D88" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="B90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="B94" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D94" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="B95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B97" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>18</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>674</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="B100" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D100" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B101" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="B102" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D104" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" t="s">
+        <v>18</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G108"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>779</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>794</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>931</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>937</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>950</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>966</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>972</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D75" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D77" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D79" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D81" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D88" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B94" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D94" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B97" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>18</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B100" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D100" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B101" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B102" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D104" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" t="s">
+        <v>18</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="12" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B105" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D105" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" t="s">
+        <v>18</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B106" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
+        <v>18</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="12" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D107" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="12" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D108" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" t="s">
+        <v>18</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G93"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D75" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D77" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D79" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D81" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D88" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>